--- a/docs/官方标准与参数设定.xlsx
+++ b/docs/官方标准与参数设定.xlsx
@@ -728,6 +728,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1029,7 +1030,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>3.5 m/处</t>
+          <t>2.0 m/处</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1039,7 +1040,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>光箱/入口端余留（2~5m 惯例）</t>
+          <t>YD/T 5102-2024 表4：交接箱/分纤箱/终端盒处预留 1~3m（取中值 2.0）</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
